--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -919,10 +919,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1096.8</v>
+        <v>1112.8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>427.5</v>
+        <v>443.5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Adrian Bors: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 10 projects x UG (16h) = 160.0h</t>
+          <t>NLPG (20cr): Adrian Bors: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 11 projects x UG (16h) = 176.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1298.6</v>
+        <v>1266.6</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PLEI (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PLEI (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -1023,10 +1023,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>911.2333333333333</v>
+        <v>927.2333333333333</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>303.8333333333333</v>
+        <v>319.8333333333333</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Alvaro Miyazawa: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>ARIA (20cr): Alvaro Miyazawa: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1123,10 +1123,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>880.9333333333333</v>
+        <v>816.9333333333333</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>459.6333333333333</v>
+        <v>395.6333333333333</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>164.2</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 11 students x 3h = 33.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 11 students x 3h = 33.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1227,10 +1227,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1030.933333333333</v>
+        <v>1014.933333333333</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>423.5333333333333</v>
+        <v>407.5333333333333</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>268.2</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1383,10 +1383,10 @@
         <v>0.4</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>460.5466666666667</v>
+        <v>444.5466666666667</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>212.8666666666667</v>
+        <v>196.8666666666667</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>177.68</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1435,10 +1435,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1156.16</v>
+        <v>1140.16</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>401.4</v>
+        <v>385.4</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>579.76</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Colin Paterson: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Colin Paterson: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 6 projects x UG (16h) = 96.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1487,10 +1487,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>657.0333333333333</v>
+        <v>545.0333333333333</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>317.8333333333334</v>
+        <v>205.8333333333333</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>164.2</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Da Li: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>LLMA (20cr): Da Li: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1591,10 +1591,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>444.8</v>
+        <v>476.8</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>164.2</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 11 projects x UG (16h) = 176.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1643,10 +1643,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1168.983333333333</v>
+        <v>1152.983333333333</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>405.3833333333333</v>
+        <v>389.3833333333333</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>260.2</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1799,10 +1799,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>553.5999999999999</v>
+        <v>521.5999999999999</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>214.4</v>
+        <v>182.4</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>164.2</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>SOF2 (20cr): Fang Yan: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>SOF2 (20cr): Fang Yan: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2163,10 +2163,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>828.8000000000001</v>
+        <v>716.8</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>407.5</v>
+        <v>295.5</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>164.2</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 25 students x 3h = 75.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2215,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1485.666666666667</v>
+        <v>1469.666666666667</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>309.8666666666667</v>
+        <v>293.8666666666667</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1000.8</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2267,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1355.5</v>
+        <v>1275.5</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>355.7</v>
+        <v>275.7</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>332.2</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2319,10 +2319,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>985.1</v>
+        <v>969.1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>297.7</v>
+        <v>281.7</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>348.2</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2471,10 +2471,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1170.233333333333</v>
+        <v>1122.233333333333</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>454.6333333333333</v>
+        <v>406.6333333333333</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>212.2</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2523,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1173.3</v>
+        <v>1205.3</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>395.8</v>
+        <v>427.8</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>356.2</v>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2575,10 +2575,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1234.7</v>
+        <v>1154.7</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>429</v>
+        <v>349</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>548.6</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2627,10 +2627,10 @@
         <v>0.8</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>734.6039999999999</v>
+        <v>662.6039999999999</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>314.7</v>
+        <v>242.7</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>227.36</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
+          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2731,10 +2731,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>901.9333333333333</v>
+        <v>757.9333333333334</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>480.6333333333333</v>
+        <v>336.6333333333333</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>164.2</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2783,10 +2783,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>816.6</v>
+        <v>928.6</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>395.3</v>
+        <v>507.3</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>164.2</v>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h</t>
+          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2887,10 +2887,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>797.3000000000001</v>
+        <v>725.3</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>376</v>
+        <v>304</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>164.2</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
+          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2939,10 +2939,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1797.633333333334</v>
+        <v>1861.633333333334</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>281.6333333333333</v>
+        <v>345.6333333333333</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>1012.6</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3043,10 +3043,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1993.32</v>
+        <v>2009.32</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>296.3</v>
+        <v>312.3</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>996.5800000000002</v>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 projects x UG (16h) = 48.0h</t>
+          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3147,10 +3147,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1702.933333333333</v>
+        <v>1878.933333333333</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>250.9333333333333</v>
+        <v>426.9333333333333</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>1112.8</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 13 projects x UG (16h) = 208.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3199,10 +3199,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1010.9</v>
+        <v>978.9</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>484.55</v>
+        <v>452.55</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>228.2</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3303,10 +3303,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1158</v>
+        <v>1134</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>378.4</v>
+        <v>354.4</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>358.3</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
+          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3407,10 +3407,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1043.88</v>
+        <v>1019.88</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>404.9</v>
+        <v>380.9</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>398.3</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
+          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3459,10 +3459,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1120.363333333333</v>
+        <v>1104.363333333333</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>611.4833333333333</v>
+        <v>595.4833333333333</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>268.2</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -3563,10 +3563,10 @@
         <v>0.8</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>648.66</v>
+        <v>600.66</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>377.3</v>
+        <v>329.3</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>131.36</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 10 projects x MSc (24h) = 240.0h</t>
+          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3615,10 +3615,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1365.366666666667</v>
+        <v>1349.366666666667</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>383.6666666666666</v>
+        <v>367.6666666666666</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>478.3</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -3719,10 +3719,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>855.1166666666666</v>
+        <v>823.1166666666666</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>403.9166666666666</v>
+        <v>371.9166666666666</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>276.2</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3819,10 +3819,10 @@
         <v>1</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>919.8333333333334</v>
+        <v>807.8333333333334</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>416.4333333333333</v>
+        <v>304.4333333333333</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>164.2</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; LLMA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; LLMA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3871,10 +3871,10 @@
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1380.45</v>
+        <v>1364.45</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>274.55</v>
+        <v>258.55</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>520.4000000000001</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3975,10 +3975,10 @@
         <v>1</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1190.5</v>
+        <v>1222.5</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>336.8</v>
+        <v>368.8</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>350.3</v>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4027,10 +4027,10 @@
         <v>1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1557.546666666667</v>
+        <v>1477.546666666667</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>624.2666666666667</v>
+        <v>544.2666666666667</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>364.2</v>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 9 projects x UG (16h) = 144.0h</t>
+          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4079,10 +4079,10 @@
         <v>1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1103.9</v>
+        <v>1079.9</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>408.5</v>
+        <v>384.5</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>356.2</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 7 projects x MSc (24h) = 168.0h</t>
+          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -4131,10 +4131,10 @@
         <v>1</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1490.316666666667</v>
+        <v>1506.316666666667</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>351.7666666666667</v>
+        <v>367.7666666666667</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>676.2</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -4183,10 +4183,10 @@
         <v>1</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>925.1</v>
+        <v>893.1</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>423.8</v>
+        <v>391.8</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>244.2</v>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -4235,10 +4235,10 @@
         <v>1</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1169.1</v>
+        <v>1233.1</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>638.7</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>; Pastoral: 9 students x 3h = 27.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>; Pastoral: 9 students x 3h = 27.0h; Projects: 4 projects x UG (16h) = 64.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -4287,10 +4287,10 @@
         <v>1</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>856.5</v>
+        <v>840.5</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>419.2</v>
+        <v>403.2</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>180.2</v>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>427.5</v>
+        <v>443.5</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>303.8333333333333</v>
+        <v>319.8333333333333</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>459.6333333333333</v>
+        <v>395.6333333333333</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>164.2</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>423.5333333333333</v>
+        <v>407.5333333333333</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>268.2</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>212.8666666666667</v>
+        <v>196.8666666666667</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>177.68</v>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>401.4</v>
+        <v>385.4</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>579.76</v>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>317.8333333333334</v>
+        <v>205.8333333333333</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>164.2</v>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>444.8</v>
+        <v>476.8</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>164.2</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>405.3833333333333</v>
+        <v>389.3833333333333</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>260.2</v>
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>214.4</v>
+        <v>182.4</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>164.2</v>
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>407.5</v>
+        <v>295.5</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>164.2</v>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>309.8666666666667</v>
+        <v>293.8666666666667</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>1000.8</v>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>355.7</v>
+        <v>275.7</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>332.2</v>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>297.7</v>
+        <v>281.7</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>348.2</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>454.6333333333333</v>
+        <v>406.6333333333333</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>212.2</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>395.8</v>
+        <v>427.8</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>356.2</v>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>429</v>
+        <v>349</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>548.6</v>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>314.7</v>
+        <v>242.7</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>227.36</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>480.6333333333333</v>
+        <v>336.6333333333333</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>164.2</v>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>395.3</v>
+        <v>507.3</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>164.2</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>376</v>
+        <v>304</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>164.2</v>
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>281.6333333333333</v>
+        <v>345.6333333333333</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>1012.6</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>296.3</v>
+        <v>312.3</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>996.5800000000002</v>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>250.9333333333333</v>
+        <v>426.9333333333333</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>1112.8</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>484.55</v>
+        <v>452.55</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>228.2</v>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>378.4</v>
+        <v>354.4</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>358.3</v>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>404.9</v>
+        <v>380.9</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>398.3</v>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>611.4833333333333</v>
+        <v>595.4833333333333</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>268.2</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>377.3</v>
+        <v>329.3</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>131.36</v>
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>383.6666666666666</v>
+        <v>367.6666666666666</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>478.3</v>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>403.9166666666666</v>
+        <v>371.9166666666666</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>276.2</v>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>416.4333333333333</v>
+        <v>304.4333333333333</v>
       </c>
       <c r="C58" s="7" t="n">
         <v>164.2</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>274.55</v>
+        <v>258.55</v>
       </c>
       <c r="C59" s="7" t="n">
         <v>520.4000000000001</v>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>336.8</v>
+        <v>368.8</v>
       </c>
       <c r="C61" s="7" t="n">
         <v>350.3</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>624.2666666666667</v>
+        <v>544.2666666666667</v>
       </c>
       <c r="C62" s="7" t="n">
         <v>364.2</v>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>408.5</v>
+        <v>384.5</v>
       </c>
       <c r="C63" s="7" t="n">
         <v>356.2</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>351.7666666666667</v>
+        <v>367.7666666666667</v>
       </c>
       <c r="C64" s="7" t="n">
         <v>676.2</v>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>423.8</v>
+        <v>391.8</v>
       </c>
       <c r="C65" s="7" t="n">
         <v>244.2</v>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="C66" s="7" t="n">
         <v>638.7</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>419.2</v>
+        <v>403.2</v>
       </c>
       <c r="C67" s="7" t="n">
         <v>180.2</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>887.4000000000001</v>
+        <v>805.3000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>548.2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Invalid FTE value for grant: '?'; Invalid FTE value for grant: '?'</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1175,13 +1175,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1176.9</v>
+        <v>848.5</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>357.3</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>644.6000000000001</v>
+        <v>316.2</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>175</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1435,13 +1435,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1140.16</v>
+        <v>844.5999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>385.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>579.76</v>
+        <v>284.2</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>175</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai (Industry): 3% of 1642h = 49.3h; Grant KTP with Advai: 5% of 1642h = 82.1h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1747,16 +1747,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1537.14</v>
+        <v>880.3400000000001</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>50.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1114.9</v>
+        <v>540.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>372.04</v>
+        <v>289.94</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 5% of 1642h = 82.1h; Grant MOSAICO: 5% of 1642h = 82.1h; Grant SCHEME: 20% of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Research Group Leader: 10% of 1642h = 164.2h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 5% of 1642h = 82.1h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1903,13 +1903,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2143.186666666667</v>
+        <v>648.9666666666667</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>91.66666666666666</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1794.42</v>
+        <v>300.2</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>257.1</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11% of 1642h = 180.6h; Grant Alan Turing AI Fellowship: 80% of 1642h = 1313.6h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1955,13 +1955,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2435.6</v>
+        <v>2107.2</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>588.6</v>
+        <v>260.2</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>1817</v>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h; Grant SCHEME: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2059,13 +2059,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1670.5</v>
+        <v>603.2</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1495.5</v>
+        <v>428.2</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>175</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 264.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant A STAR TO STEER BY: 5% of 1642h = 82.1h; Grant The Centre for Assuring Autonomy: 40% of 1642h = 656.8h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2111,13 +2111,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>828.7333333333333</v>
+        <v>746.6333333333334</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>243.2333333333333</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>246.3</v>
+        <v>164.2</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>339.2</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5% of 1642h = 82.1h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2215,13 +2215,13 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1469.666666666667</v>
+        <v>977.0666666666666</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>293.8666666666667</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1000.8</v>
+        <v>508.2</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>175</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant Smart Data Donation Service (SDDS): 10% of 1642h = 164.2h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2423,26 +2423,26 @@
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1878.9</v>
+        <v>565.3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1539.7</v>
+        <v>308.2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h; Grant Assessment of DSTA USVs and Continual Assurance of CI/CD for USVs: 5% of 1642h = 82.1h; Grant RAI UK: Safety &amp; Security Network (SSAIN): 20% of 1642h = 328.4h; Grant The Centre for Assuring Autonomy: 50% of 1642h = 821.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1154.7</v>
+        <v>826.3000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>349</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>548.6</v>
+        <v>220.2</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>257.1</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10% of 1642h = 164.2h; Grant SCHEME: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2939,16 +2939,16 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1861.633333333334</v>
+        <v>1451.133333333333</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>345.6333333333333</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1012.6</v>
+        <v>684.2</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>503.4</v>
+        <v>421.3</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0% of 1642h = 0.0h; Grant IGGI: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2991,13 +2991,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1296.3</v>
+        <v>967.9000000000001</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>312.5</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>644.6</v>
+        <v>316.2</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>339.2</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20% of 1642h = 328.4h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -3043,16 +3043,16 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2009.32</v>
+        <v>1286.84</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>312.3</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>996.5800000000002</v>
+        <v>356.2</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>700.4400000000001</v>
+        <v>618.34</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Intelligent Dependable Environment Control for Sustainable Aquaculture: 20% of 1642h = 328.4h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9% of 1642h = 147.8h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5% of 1642h = 82.1h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Graduate Chair: 20% of 1642h = 328.4h; Research Group Leader: 10% of 1642h = 164.2h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate Chair: 20% of 1642h = 328.4h; Research Group Leader: 5% of 1642h = 82.1h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -3147,13 +3147,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1878.933333333333</v>
+        <v>1386.333333333333</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>426.9333333333333</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1112.8</v>
+        <v>620.2</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>339.2</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5% of 1642h = 82.1h; Grant REMOTE: Resilient and Secure Multi-Access Interoperable Communication Fabric for TinyEdge: 20% of 1642h = 328.4h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -3251,13 +3251,13 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1257.54</v>
+        <v>847.0400000000001</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>918.7</v>
+        <v>508.2</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>207.84</v>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant ARISE: Accelerating ReIntroduction of EcoSystem-Engineering Ant Colonies with Embodied AI: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -3303,13 +3303,13 @@
         <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1134</v>
+        <v>1051.9</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>354.4</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>358.3</v>
+        <v>276.2</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>421.3</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -3355,7 +3355,7 @@
         <v>0.6</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>657.04</v>
+        <v>607.78</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>3</v>
@@ -3364,7 +3364,7 @@
         <v>450.52</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>203.52</v>
+        <v>154.26</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>ART staff representative: 0% of 985h = 0.0h; Research Group Leader: 10% of 985h = 98.5h; Engagement (email/meetings): 60.0h; Personal development: 45.0h (FTE: 0.60)</t>
+          <t>ART staff representative: 0% of 985h = 0.0h; Research Group Leader: 5% of 985h = 49.3h; Engagement (email/meetings): 60.0h; Personal development: 45.0h (FTE: 0.60)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3407,13 +3407,13 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1019.88</v>
+        <v>937.78</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>380.9</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>398.3</v>
+        <v>316.2</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>240.68</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3615,16 +3615,16 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1349.366666666667</v>
+        <v>1185.166666666667</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>367.6666666666666</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>478.3</v>
+        <v>396.2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>503.4</v>
+        <v>421.3</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3667,13 +3667,13 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1020.24</v>
+        <v>576.9</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>53.7</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>791.54</v>
+        <v>348.2</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>175</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h; Grant Verifiable generation of SOTIF requirements: 2% of 1642h = 32.8h; Grant Moving forward explainable AI by combining different assurance metrics: 15% of 1642h = 246.3h; Grant AI safety argumentation review: 5% of 1642h = 82.1h; Grant KTP with DNV Services Ltd - Innovate part: 3% of 1642h = 49.3h; Grant KTP with DNV Services Ltd - Industry part: 2% of 1642h = 32.8h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -3771,13 +3771,13 @@
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1309.68</v>
+        <v>620.04</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1101.84</v>
+        <v>412.2</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>207.84</v>
@@ -3785,7 +3785,7 @@
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h; Grant Human-centric Digital Twin Approaches to Trustworthy AI and Robotics for Improved Working Conditions: 12% of 1642h = 197.0h; Grant Socially-Acceptable and Trustworthy Human-Robot Teaming for Agile Industries (SYMPHONY Resubmission): 10% of 1642h = 164.2h; Grant GuardAI ( Enhancing Robustness and Security of Edge AI Systems for Safety-Critical Applications): 15% of 1642h = 246.3h; Grant MOSAICO: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3871,16 +3871,16 @@
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1364.45</v>
+        <v>1118.15</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>258.55</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>520.4000000000001</v>
+        <v>356.2</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>585.5</v>
+        <v>503.4</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10% of 1642h = 164.2h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -3975,13 +3975,13 @@
         <v>1</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1222.5</v>
+        <v>1140.4</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>368.8</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>350.3</v>
+        <v>268.2</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>503.4</v>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant SCHEME: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -4131,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1506.316666666667</v>
+        <v>1424.216666666667</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>367.7666666666667</v>
@@ -4140,7 +4140,7 @@
         <v>676.2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>462.35</v>
+        <v>380.25</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Research Group Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -4235,13 +4235,13 @@
         <v>1</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1233.1</v>
+        <v>822.6</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>91</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>638.7</v>
+        <v>228.2</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>503.4</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10% of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10% of 1642h = 164.2h; Grant The Centre for Assuring Autonomy: 5% of 1642h = 82.1h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -4464,7 +4464,7 @@
         <v>548.2</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(B5:D5)</f>
@@ -4501,7 +4501,7 @@
         <v>357.3</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>644.6000000000001</v>
+        <v>316.2</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>175</v>
@@ -4601,7 +4601,7 @@
         <v>385.4</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>579.76</v>
+        <v>284.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>175</v>
@@ -4721,10 +4721,10 @@
         <v>50.2</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1114.9</v>
+        <v>540.2</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>372.04</v>
+        <v>289.94</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(B18:D18)</f>
@@ -4781,7 +4781,7 @@
         <v>91.66666666666666</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1794.42</v>
+        <v>300.2</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>257.1</v>
@@ -4801,7 +4801,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>588.6</v>
+        <v>260.2</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1817</v>
@@ -4841,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1495.5</v>
+        <v>428.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>175</v>
@@ -4861,7 +4861,7 @@
         <v>243.2333333333333</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>246.3</v>
+        <v>164.2</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>339.2</v>
@@ -4901,7 +4901,7 @@
         <v>293.8666666666667</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>1000.8</v>
+        <v>508.2</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>175</v>
@@ -4981,10 +4981,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>1539.7</v>
+        <v>308.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -5041,7 +5041,7 @@
         <v>349</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>548.6</v>
+        <v>220.2</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>257.1</v>
@@ -5181,10 +5181,10 @@
         <v>345.6333333333333</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>1012.6</v>
+        <v>684.2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>503.4</v>
+        <v>421.3</v>
       </c>
       <c r="E41" s="7">
         <f>SUM(B41:D41)</f>
@@ -5201,7 +5201,7 @@
         <v>312.5</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>644.6</v>
+        <v>316.2</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>339.2</v>
@@ -5221,10 +5221,10 @@
         <v>312.3</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>996.5800000000002</v>
+        <v>356.2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>700.4400000000001</v>
+        <v>618.34</v>
       </c>
       <c r="E43" s="7">
         <f>SUM(B43:D43)</f>
@@ -5261,7 +5261,7 @@
         <v>426.9333333333333</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>1112.8</v>
+        <v>620.2</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>339.2</v>
@@ -5301,7 +5301,7 @@
         <v>131</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>918.7</v>
+        <v>508.2</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>207.84</v>
@@ -5321,7 +5321,7 @@
         <v>354.4</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>358.3</v>
+        <v>276.2</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>421.3</v>
@@ -5344,7 +5344,7 @@
         <v>450.52</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>203.52</v>
+        <v>154.26</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -5361,7 +5361,7 @@
         <v>380.9</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>398.3</v>
+        <v>316.2</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>240.68</v>
@@ -5441,10 +5441,10 @@
         <v>367.6666666666666</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>478.3</v>
+        <v>396.2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>503.4</v>
+        <v>421.3</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -5461,7 +5461,7 @@
         <v>53.7</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>791.54</v>
+        <v>348.2</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>175</v>
@@ -5501,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>1101.84</v>
+        <v>412.2</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>207.84</v>
@@ -5541,10 +5541,10 @@
         <v>258.55</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>520.4000000000001</v>
+        <v>356.2</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>585.5</v>
+        <v>503.4</v>
       </c>
       <c r="E59" s="7">
         <f>SUM(B59:D59)</f>
@@ -5581,7 +5581,7 @@
         <v>368.8</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>350.3</v>
+        <v>268.2</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>503.4</v>
@@ -5644,7 +5644,7 @@
         <v>676.2</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>462.35</v>
+        <v>380.25</v>
       </c>
       <c r="E64" s="7">
         <f>SUM(B64:D64)</f>
@@ -5681,7 +5681,7 @@
         <v>91</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>638.7</v>
+        <v>228.2</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>503.4</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -195,12 +195,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$67</f>
+              <f>'Staff Workload'!$A$2:$A$64</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$D$2:$D$67</f>
+              <f>'Staff Workload'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -219,12 +219,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$67</f>
+              <f>'Staff Workload'!$A$2:$A$64</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$E$2:$E$67</f>
+              <f>'Staff Workload'!$E$2:$E$64</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Staff Workload'!$A$2:$A$67</f>
+              <f>'Staff Workload'!$A$2:$A$64</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Staff Workload'!$F$2:$F$67</f>
+              <f>'Staff Workload'!$F$2:$F$64</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$67</f>
+              <f>'Detailed Breakdown'!$A$2:$A$64</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$B$2:$B$67</f>
+              <f>'Detailed Breakdown'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +384,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$67</f>
+              <f>'Detailed Breakdown'!$A$2:$A$64</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$C$2:$C$67</f>
+              <f>'Detailed Breakdown'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -408,12 +408,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Detailed Breakdown'!$A$2:$A$67</f>
+              <f>'Detailed Breakdown'!$A$2:$A$64</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Detailed Breakdown'!$D$2:$D$67</f>
+              <f>'Detailed Breakdown'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1844,37 +1844,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>458.2</v>
+        <v>648.9666666666667</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>71</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>212.2</v>
+        <v>300.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>SAIL (20cr): Felix Ulrich-Oltean: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>LLMA (20cr): Frank Soboczenski: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1896,37 +1896,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>648.9666666666667</v>
+        <v>2107.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>91.66666666666666</v>
+        <v>30</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>300.2</v>
+        <v>260.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>257.1</v>
+        <v>1817</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>LLMA (20cr): Frank Soboczenski: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>; Pastoral: 10 students x 3h = 30.0h</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1948,37 +1948,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2107.2</v>
+        <v>1444</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>30</v>
+        <v>99.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>260.2</v>
+        <v>348.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1817</v>
+        <v>996</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>; Pastoral: 10 students x 3h = 30.0h</t>
+          <t>EMBS (20cr): Ian Gray: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x assessor (8h each) = 96.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Head of Department: 100% of 1642h = 1642.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -2000,37 +2000,37 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Ibrahim Habli</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1444</v>
+        <v>603.2</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>99.8</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>348.2</v>
+        <v>428.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>996</v>
+        <v>175</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Ian Gray: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>; Also teaches: Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head of Department (On-campus teaching): 50% of 1642h = 821.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2052,37 +2052,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Ibrahim Habli</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>603.2</v>
+        <v>746.6333333333334</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>243.2333333333333</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>; Also teaches: Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
+          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 264.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2104,27 +2104,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>746.6333333333334</v>
+        <v>716.8</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>243.2333333333333</v>
+        <v>295.5</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>164.2</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>IMLO (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 25 students x 3h = 75.0h</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Taught Project Coordinator: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2156,37 +2156,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>716.8</v>
+        <v>977.0666666666666</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>295.5</v>
+        <v>293.8666666666667</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>164.2</v>
+        <v>508.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Stovold: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 25 students x 3h = 75.0h</t>
+          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2208,37 +2208,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>977.0666666666666</v>
+        <v>1275.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>293.8666666666667</v>
+        <v>275.7</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>508.2</v>
+        <v>332.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>175</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>DEC Chair: 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2260,37 +2260,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1275.5</v>
+        <v>969.1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>275.7</v>
+        <v>281.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>332.2</v>
+        <v>348.2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>667.5999999999999</v>
+        <v>339.2</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 168.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>DEC Chair: 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -2312,37 +2312,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>969.1</v>
+        <v>750.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>281.7</v>
+        <v>347.1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>348.2</v>
+        <v>228.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ECR representative: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2364,37 +2364,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>John McDermid</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>750.3</v>
+        <v>565.3</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>347.1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>228.2</v>
+        <v>308.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
-        </is>
-      </c>
+        <v>257.1</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>ECR representative: 0% of 1642h = 0.0h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -2416,33 +2412,37 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>John McDermid</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>565.3</v>
+        <v>1122.233333333333</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>406.6333333333333</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>308.2</v>
+        <v>212.2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
+        <v>503.4</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -2464,37 +2464,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1122.233333333333</v>
+        <v>1205.3</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>406.6333333333333</v>
+        <v>427.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>212.2</v>
+        <v>356.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>503.4</v>
+        <v>421.3</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE = 48.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Director of Students: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2516,37 +2516,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1205.3</v>
+        <v>826.3000000000001</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>427.8</v>
+        <v>349</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>356.2</v>
+        <v>220.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>421.3</v>
+        <v>257.1</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Deputy Director of Admissions (UG Admissions): 15% of 1642h = 246.3h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>PGR Training Officer: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2568,37 +2568,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Mark Nicholson</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>826.3000000000001</v>
+        <v>662.6039999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>349</v>
+        <v>242.7</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>220.2</v>
+        <v>227.36</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>257.1</v>
+        <v>192.544</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE = 96.0h</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>PGR Training Officer: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>StAMP committee: 4% of 1314h = 52.5h; Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2620,37 +2620,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Mark Nicholson</t>
+          <t>Mark Sujan</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>662.6039999999999</v>
+        <v>318.76</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>242.7</v>
+        <v>47.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>227.36</v>
+        <v>131.36</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>192.544</v>
+        <v>140</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
+          <t>HUFS (10cr): Mark Sujan: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE = 96.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee: 4% of 1314h = 52.5h; Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
+          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2672,27 +2672,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Mark Sujan</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>318.76</v>
+        <v>757.9333333333334</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>47.4</v>
+        <v>336.6333333333333</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>131.36</v>
+        <v>164.2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>140</v>
+        <v>257.1</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>HUFS (10cr): Mark Sujan: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
+          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
+          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2724,17 +2724,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>757.9333333333334</v>
+        <v>928.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>336.6333333333333</v>
+        <v>507.3</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>164.2</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Mike Freeman: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h</t>
+          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Academic Admissions Team: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2776,37 +2776,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>928.6</v>
+        <v>1468.933333333333</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>507.3</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -2828,37 +2828,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Oleg Lisagor</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1468.933333333333</v>
+        <v>725.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>208.9333333333333</v>
+        <v>304</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>831.8000000000001</v>
+        <v>257.1</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 264.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Deputy Head (Research): 40% of 1642h = 656.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -2880,37 +2880,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Oleg Lisagor</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>725.3</v>
+        <v>1451.133333333333</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>304</v>
+        <v>345.6333333333333</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>164.2</v>
+        <v>684.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2932,37 +2932,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1451.133333333333</v>
+        <v>967.9000000000001</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>345.6333333333333</v>
+        <v>312.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>684.2</v>
+        <v>316.2</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>421.3</v>
+        <v>339.2</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; REF Lead: 5% of 1642h = 82.1h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2984,37 +2984,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>967.9000000000001</v>
+        <v>1286.84</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>312.5</v>
+        <v>312.3</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>316.2</v>
+        <v>356.2</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>339.2</v>
+        <v>618.34</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate Chair: 20% of 1642h = 328.4h; Research Group Leader: 5% of 1642h = 82.1h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -3036,37 +3036,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1286.84</v>
+        <v>1069.866666666667</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>312.3</v>
+        <v>430.4666666666666</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>356.2</v>
+        <v>300.2</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>618.34</v>
+        <v>339.2</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Graduate Chair: 20% of 1642h = 328.4h; Research Group Leader: 5% of 1642h = 82.1h; Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3088,37 +3088,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1069.866666666667</v>
+        <v>1386.333333333333</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>430.4666666666666</v>
+        <v>426.9333333333333</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>300.2</v>
+        <v>620.2</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>339.2</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 13 projects x UG (16h) = 208.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>UG PL: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3140,37 +3140,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1386.333333333333</v>
+        <v>978.9</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>426.9333333333333</v>
+        <v>452.55</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>620.2</v>
+        <v>228.2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>339.2</v>
+        <v>298.15</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 13 projects x UG (16h) = 208.0h</t>
+          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
@@ -3192,37 +3192,37 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>978.9</v>
+        <v>847.0400000000001</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>452.55</v>
+        <v>131</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>228.2</v>
+        <v>508.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>298.15</v>
+        <v>207.84</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Graduate School Board (Ordinary member): 2% of 1642h = 41.1h; Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -3244,37 +3244,37 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Richard Hawkins</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>847.0400000000001</v>
+        <v>1051.9</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>131</v>
+        <v>354.4</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>508.2</v>
+        <v>276.2</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>207.84</v>
+        <v>421.3</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Impact: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -3296,37 +3296,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Richard Hawkins</t>
+          <t>Richard Wilson</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1051.9</v>
+        <v>607.78</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>354.4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>276.2</v>
+        <v>450.52</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>421.3</v>
+        <v>154.26</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
+          <t>; Pastoral: 1 students x 3h = 3.0h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 352.0h</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Impact: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>ART staff representative: 0% of 985h = 0.0h; Research Group Leader: 5% of 985h = 49.3h; Engagement (email/meetings): 60.0h; Personal development: 45.0h (FTE: 0.60)</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
@@ -3348,37 +3348,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Richard Wilson</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>607.78</v>
+        <v>937.78</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3</v>
+        <v>380.9</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>450.52</v>
+        <v>316.2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>154.26</v>
+        <v>240.68</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>; Pastoral: 1 students x 3h = 3.0h; Also teaches: Artificial Intelligence (AI) (SAINTS - not included in workload)</t>
+          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 352.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>ART staff representative: 0% of 985h = 0.0h; Research Group Leader: 5% of 985h = 49.3h; Engagement (email/meetings): 60.0h; Personal development: 45.0h (FTE: 0.60)</t>
+          <t>StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -3400,32 +3400,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>937.78</v>
+        <v>1104.363333333333</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>380.9</v>
+        <v>595.4833333333333</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>316.2</v>
+        <v>268.2</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>240.68</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
+          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3452,37 +3452,37 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1104.363333333333</v>
+        <v>623.7833333333333</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>595.4833333333333</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>240.68</v>
+        <v>175</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -3504,27 +3504,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Sarah Carrington</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>623.7833333333333</v>
+        <v>600.66</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>284.5833333333333</v>
+        <v>329.3</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>164.2</v>
+        <v>131.36</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -3556,37 +3556,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Sarah Carrington</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>600.66</v>
+        <v>1185.166666666667</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>329.3</v>
+        <v>367.6666666666666</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>131.36</v>
+        <v>396.2</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>140</v>
+        <v>421.3</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
+          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
+          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -3608,37 +3608,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1185.166666666667</v>
+        <v>823.1166666666666</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>367.6666666666666</v>
+        <v>371.9166666666666</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>396.2</v>
+        <v>276.2</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Deputy Graduate Chair: 10% of 1642h = 164.2h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No administrative roles assigned</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -3660,37 +3660,33 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Simon Burton</t>
+          <t>Simos Gerasimou</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>576.9</v>
+        <v>620.04</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>53.7</v>
+        <v>0</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>348.2</v>
+        <v>412.2</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>CASA (10cr): Simon Burton: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h</t>
-        </is>
-      </c>
+        <v>207.84</v>
+      </c>
+      <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -3700,7 +3696,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -3712,37 +3708,37 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>823.1166666666666</v>
+        <v>807.8333333333334</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>371.9166666666666</v>
+        <v>304.4333333333333</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>276.2</v>
+        <v>164.2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; LLMA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>No research activities recorded</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Mumbai Campus Partnership Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
@@ -3752,7 +3748,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -3764,33 +3760,37 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Simos Gerasimou</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>620.04</v>
+        <v>1118.15</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>258.55</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>412.2</v>
+        <v>356.2</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>207.84</v>
-      </c>
-      <c r="G57" s="4" t="inlineStr"/>
+        <v>503.4</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+        </is>
+      </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Research Mentor: 2% of 1642h = 32.8h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
@@ -3812,37 +3812,37 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>807.8333333333334</v>
+        <v>1353.8</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>304.4333333333333</v>
+        <v>234</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>164.2</v>
+        <v>452.2</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>339.2</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Soumya Banerjee: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; LLMA (20cr): Soumya Banerjee: New lecturer + new content (7.5x): 0.0h base @ 2.5x + 0.0h content dev; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h</t>
+          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Mumbai Campus Partnership Leader: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>CBoE (on-campus): 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>LLMA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -3864,37 +3864,37 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1118.15</v>
+        <v>1140.4</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>258.55</v>
+        <v>368.8</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>356.2</v>
+        <v>268.2</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>503.4</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Progression Panel Chair: 15% of 1642h = 246.3h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -3916,37 +3916,37 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1353.8</v>
+        <v>1477.546666666667</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>234</v>
+        <v>544.2666666666667</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>452.2</v>
+        <v>364.2</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>667.5999999999999</v>
+        <v>569.08</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>CBoE (on-campus): 30% of 1642h = 492.6h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>CSCSE HAP Partnership Leader: 10% of 1642h = 164.2h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -3968,37 +3968,37 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1140.4</v>
+        <v>1079.9</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>368.8</v>
+        <v>384.5</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>268.2</v>
+        <v>356.2</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>503.4</v>
+        <v>339.2</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>Student Disability Representative: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -4020,37 +4020,37 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1477.546666666667</v>
+        <v>1424.216666666667</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>544.2666666666667</v>
+        <v>367.7666666666667</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>364.2</v>
+        <v>676.2</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>569.08</v>
+        <v>380.25</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 200.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>CSCSE HAP Partnership Leader: 10% of 1642h = 164.2h; Deputy CBoEs: 10% of 1642h = 164.2h; StAMP committee: 4% of 1642h = 65.7h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>ARIA: no student numbers in CS Module Numbers.csv - marking hours estimated from a default of 100 students</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -4072,37 +4072,37 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1079.9</v>
+        <v>893.1</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>384.5</v>
+        <v>391.8</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>356.2</v>
+        <v>244.2</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
+          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Deputy CBoEs: 10% of 1642h = 164.2h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -4124,37 +4124,37 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1424.216666666667</v>
+        <v>840.5</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>367.7666666666667</v>
+        <v>403.2</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>676.2</v>
+        <v>180.2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>380.25</v>
+        <v>257.1</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Director of Admissions: 5% of 1642h = 82.1h; Internally Distributed Funding panel reviewer: 2% of 1642h = 41.1h; Research Group Leader: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
+          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -4168,162 +4168,6 @@
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Xinwei Fang</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>893.1</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>391.8</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>244.2</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Yan Jia</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>822.6</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>228.2</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>503.4</v>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>; Pastoral: 9 students x 3h = 27.0h; Projects: 4 projects x UG (16h) = 64.0h; Also teaches: Designing Safe AI (Safe AI 2), Foundations of Safe AI (Safe AI 1) (SAINTS - not included in workload)</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 64.0h</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>Ethics Committee Member: 20% of 1642h = 328.4h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Yuchen Zhao</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>840.5</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>403.2</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>180.2</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>PhD supervision: 2x assessor (8h each) = 16.0h</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>Other PLs: 5% of 1642h = 82.1h; Engagement (email/meetings): 100.0h; Personal development: 75.0h (FTE: 1.00)</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4354,7 +4198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4754,17 +4598,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Felix Ulrich-Oltean</t>
+          <t>Frank Soboczenski</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>71</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>212.2</v>
+        <v>300.2</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
@@ -4774,17 +4618,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Frank Soboczenski</t>
+          <t>Iain Bate</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>91.66666666666666</v>
+        <v>30</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>300.2</v>
+        <v>260.2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>257.1</v>
+        <v>1817</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
@@ -4794,17 +4638,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Iain Bate</t>
+          <t>Ian Gray</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>30</v>
+        <v>99.8</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>260.2</v>
+        <v>348.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1817</v>
+        <v>996</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
@@ -4814,17 +4658,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ian Gray</t>
+          <t>Ibrahim Habli</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>99.8</v>
+        <v>0</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>348.2</v>
+        <v>428.2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>996</v>
+        <v>175</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
@@ -4834,17 +4678,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ibrahim Habli</t>
+          <t>Jacob Rigby</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>0</v>
+        <v>243.2333333333333</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
@@ -4854,17 +4698,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jacob Rigby</t>
+          <t>James Stovold</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>243.2333333333333</v>
+        <v>295.5</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>164.2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
@@ -4874,17 +4718,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Stovold</t>
+          <t>James Walker</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>295.5</v>
+        <v>293.8666666666667</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>164.2</v>
+        <v>508.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>257.1</v>
+        <v>175</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
@@ -4894,17 +4738,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>James Walker</t>
+          <t>Jen Beeston</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>293.8666666666667</v>
+        <v>275.7</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>508.2</v>
+        <v>332.2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>175</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
@@ -4914,17 +4758,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jen Beeston</t>
+          <t>Jo Iacovides</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>275.7</v>
+        <v>281.7</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>332.2</v>
+        <v>348.2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>667.5999999999999</v>
+        <v>339.2</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
@@ -4934,17 +4778,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jo Iacovides</t>
+          <t>Joe Cutting</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>281.7</v>
+        <v>347.1</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>348.2</v>
+        <v>228.2</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>339.2</v>
+        <v>175</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
@@ -4954,17 +4798,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Joe Cutting</t>
+          <t>John McDermid</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>347.1</v>
+        <v>0</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>228.2</v>
+        <v>308.2</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>175</v>
+        <v>257.1</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
@@ -4974,17 +4818,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>John McDermid</t>
+          <t>Katrina Attwood</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0</v>
+        <v>406.6333333333333</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>308.2</v>
+        <v>212.2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>257.1</v>
+        <v>503.4</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(B31:D31)</f>
@@ -4994,17 +4838,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Katrina Attwood</t>
+          <t>Kofi Appiah</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>406.6333333333333</v>
+        <v>427.8</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>212.2</v>
+        <v>356.2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>503.4</v>
+        <v>421.3</v>
       </c>
       <c r="E32" s="7">
         <f>SUM(B32:D32)</f>
@@ -5014,17 +4858,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kofi Appiah</t>
+          <t>Kostas Barmpis</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>427.8</v>
+        <v>349</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>356.2</v>
+        <v>220.2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>421.3</v>
+        <v>257.1</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(B33:D33)</f>
@@ -5034,17 +4878,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kostas Barmpis</t>
+          <t>Mark Nicholson</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>349</v>
+        <v>242.7</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>220.2</v>
+        <v>227.36</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>257.1</v>
+        <v>192.544</v>
       </c>
       <c r="E34" s="7">
         <f>SUM(B34:D34)</f>
@@ -5054,17 +4898,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mark Nicholson</t>
+          <t>Mark Sujan</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>242.7</v>
+        <v>47.4</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>227.36</v>
+        <v>131.36</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>192.544</v>
+        <v>140</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(B35:D35)</f>
@@ -5074,17 +4918,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mark Sujan</t>
+          <t>Mike Freeman</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>47.4</v>
+        <v>336.6333333333333</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>131.36</v>
+        <v>164.2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>140</v>
+        <v>257.1</v>
       </c>
       <c r="E36" s="7">
         <f>SUM(B36:D36)</f>
@@ -5094,11 +4938,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mike Freeman</t>
+          <t>Mike O'Dea</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>336.6333333333333</v>
+        <v>507.3</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>164.2</v>
@@ -5114,17 +4958,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mike O'Dea</t>
+          <t>Nick Pears</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>507.3</v>
+        <v>208.9333333333333</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>164.2</v>
+        <v>428.2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>257.1</v>
+        <v>831.8000000000001</v>
       </c>
       <c r="E38" s="7">
         <f>SUM(B38:D38)</f>
@@ -5134,17 +4978,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nick Pears</t>
+          <t>Oleg Lisagor</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>208.9333333333333</v>
+        <v>304</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>428.2</v>
+        <v>164.2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>831.8000000000001</v>
+        <v>257.1</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(B39:D39)</f>
@@ -5154,17 +4998,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Oleg Lisagor</t>
+          <t>Paul Cairns</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>304</v>
+        <v>345.6333333333333</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>164.2</v>
+        <v>684.2</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>257.1</v>
+        <v>421.3</v>
       </c>
       <c r="E40" s="7">
         <f>SUM(B40:D40)</f>
@@ -5174,17 +5018,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Paul Cairns</t>
+          <t>Pedro Ribeiro</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>345.6333333333333</v>
+        <v>312.5</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>684.2</v>
+        <v>316.2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>421.3</v>
+        <v>339.2</v>
       </c>
       <c r="E41" s="7">
         <f>SUM(B41:D41)</f>
@@ -5194,17 +5038,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pedro Ribeiro</t>
+          <t>Pengcheng Liu</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>312.5</v>
+        <v>312.3</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>316.2</v>
+        <v>356.2</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>339.2</v>
+        <v>618.34</v>
       </c>
       <c r="E42" s="7">
         <f>SUM(B42:D42)</f>
@@ -5214,17 +5058,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pengcheng Liu</t>
+          <t>Peter Nightingale</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>312.3</v>
+        <v>430.4666666666666</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>356.2</v>
+        <v>300.2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>618.34</v>
+        <v>339.2</v>
       </c>
       <c r="E43" s="7">
         <f>SUM(B43:D43)</f>
@@ -5234,14 +5078,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Peter Nightingale</t>
+          <t>Poonam Yadav</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>430.4666666666666</v>
+        <v>426.9333333333333</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>300.2</v>
+        <v>620.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>339.2</v>
@@ -5254,17 +5098,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poonam Yadav</t>
+          <t>Pourya Shamsolmoali</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>426.9333333333333</v>
+        <v>452.55</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>620.2</v>
+        <v>228.2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>339.2</v>
+        <v>298.15</v>
       </c>
       <c r="E45" s="7">
         <f>SUM(B45:D45)</f>
@@ -5274,17 +5118,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pourya Shamsolmoali</t>
+          <t>Radu Calinescu</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>452.55</v>
+        <v>131</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>228.2</v>
+        <v>508.2</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>298.15</v>
+        <v>207.84</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(B46:D46)</f>
@@ -5294,17 +5138,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Radu Calinescu</t>
+          <t>Richard Hawkins</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>131</v>
+        <v>354.4</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>508.2</v>
+        <v>276.2</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>207.84</v>
+        <v>421.3</v>
       </c>
       <c r="E47" s="7">
         <f>SUM(B47:D47)</f>
@@ -5314,17 +5158,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Richard Hawkins</t>
+          <t>Richard Wilson</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>354.4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>276.2</v>
+        <v>450.52</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>421.3</v>
+        <v>154.26</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(B48:D48)</f>
@@ -5334,17 +5178,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Richard Wilson</t>
+          <t>Rob Alexander</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>3</v>
+        <v>380.9</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>450.52</v>
+        <v>316.2</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>154.26</v>
+        <v>240.68</v>
       </c>
       <c r="E49" s="7">
         <f>SUM(B49:D49)</f>
@@ -5354,14 +5198,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rob Alexander</t>
+          <t>Roberto Metere</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>380.9</v>
+        <v>595.4833333333333</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>316.2</v>
+        <v>268.2</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>240.68</v>
@@ -5374,17 +5218,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Roberto Metere</t>
+          <t>Sam Braunstein</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>595.4833333333333</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>268.2</v>
+        <v>164.2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>240.68</v>
+        <v>175</v>
       </c>
       <c r="E51" s="7">
         <f>SUM(B51:D51)</f>
@@ -5394,17 +5238,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sam Braunstein</t>
+          <t>Sarah Carrington</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>284.5833333333333</v>
+        <v>329.3</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>164.2</v>
+        <v>131.36</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="E52" s="7">
         <f>SUM(B52:D52)</f>
@@ -5414,17 +5258,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sarah Carrington</t>
+          <t>Siamak Shahandashti</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>329.3</v>
+        <v>367.6666666666666</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>131.36</v>
+        <v>396.2</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>140</v>
+        <v>421.3</v>
       </c>
       <c r="E53" s="7">
         <f>SUM(B53:D53)</f>
@@ -5434,17 +5278,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Siamak Shahandashti</t>
+          <t>Simon Foster</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>367.6666666666666</v>
+        <v>371.9166666666666</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>396.2</v>
+        <v>276.2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>421.3</v>
+        <v>175</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(B54:D54)</f>
@@ -5454,17 +5298,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Simon Burton</t>
+          <t>Simos Gerasimou</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>53.7</v>
+        <v>0</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>348.2</v>
+        <v>412.2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>175</v>
+        <v>207.84</v>
       </c>
       <c r="E55" s="7">
         <f>SUM(B55:D55)</f>
@@ -5474,17 +5318,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Simon Foster</t>
+          <t>Soumya Banerjee</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>371.9166666666666</v>
+        <v>304.4333333333333</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>276.2</v>
+        <v>164.2</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>175</v>
+        <v>339.2</v>
       </c>
       <c r="E56" s="7">
         <f>SUM(B56:D56)</f>
@@ -5494,17 +5338,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Simos Gerasimou</t>
+          <t>Stefano Pirandola</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0</v>
+        <v>258.55</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>412.2</v>
+        <v>356.2</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>207.84</v>
+        <v>503.4</v>
       </c>
       <c r="E57" s="7">
         <f>SUM(B57:D57)</f>
@@ -5514,17 +5358,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Soumya Banerjee</t>
+          <t>Steven Wright</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>304.4333333333333</v>
+        <v>234</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>164.2</v>
+        <v>452.2</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>339.2</v>
+        <v>667.5999999999999</v>
       </c>
       <c r="E58" s="7">
         <f>SUM(B58:D58)</f>
@@ -5534,14 +5378,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Stefano Pirandola</t>
+          <t>Steven Xiaotian Dai</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>258.55</v>
+        <v>368.8</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>356.2</v>
+        <v>268.2</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>503.4</v>
@@ -5554,17 +5398,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Steven Wright</t>
+          <t>Tommy Yuan</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>234</v>
+        <v>544.2666666666667</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>452.2</v>
+        <v>364.2</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>667.5999999999999</v>
+        <v>569.08</v>
       </c>
       <c r="E60" s="7">
         <f>SUM(B60:D60)</f>
@@ -5574,17 +5418,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Steven Xiaotian Dai</t>
+          <t>Vasileios Vasilakis</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>368.8</v>
+        <v>384.5</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>268.2</v>
+        <v>356.2</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>503.4</v>
+        <v>339.2</v>
       </c>
       <c r="E61" s="7">
         <f>SUM(B61:D61)</f>
@@ -5594,17 +5438,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tommy Yuan</t>
+          <t>William Smith</t>
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>544.2666666666667</v>
+        <v>367.7666666666667</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>364.2</v>
+        <v>676.2</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>569.08</v>
+        <v>380.25</v>
       </c>
       <c r="E62" s="7">
         <f>SUM(B62:D62)</f>
@@ -5614,17 +5458,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Vasileios Vasilakis</t>
+          <t>Xinwei Fang</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>384.5</v>
+        <v>391.8</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>356.2</v>
+        <v>244.2</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>339.2</v>
+        <v>257.1</v>
       </c>
       <c r="E63" s="7">
         <f>SUM(B63:D63)</f>
@@ -5634,80 +5478,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>William Smith</t>
+          <t>Yuchen Zhao</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>367.7666666666667</v>
+        <v>403.2</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>676.2</v>
+        <v>180.2</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>380.25</v>
+        <v>257.1</v>
       </c>
       <c r="E64" s="7">
         <f>SUM(B64:D64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Xinwei Fang</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="n">
-        <v>391.8</v>
-      </c>
-      <c r="C65" s="7" t="n">
-        <v>244.2</v>
-      </c>
-      <c r="D65" s="7" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="E65" s="7">
-        <f>SUM(B65:D65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Yan Jia</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>228.2</v>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>503.4</v>
-      </c>
-      <c r="E66" s="7">
-        <f>SUM(B66:D66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Yuchen Zhao</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n">
-        <v>403.2</v>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>180.2</v>
-      </c>
-      <c r="D67" s="7" t="n">
-        <v>257.1</v>
-      </c>
-      <c r="E67" s="7">
-        <f>SUM(B67:D67)</f>
         <v/>
       </c>
     </row>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -1075,13 +1075,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>805.3000000000001</v>
+        <v>969.5000000000001</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>548.2</v>
+        <v>712.4000000000001</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>257.1</v>
@@ -1089,7 +1089,7 @@
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 8x part-time PhD student × 48h/FTE = 384.0h</t>
+          <t>PhD supervision: 8x part-time PhD student × 48h/FTE = 384.0h; Grant RAEng Internships: 0 of 1642h = 0.0h; Grant DOMINOS: Disruption Mitigation for Responsible AI: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -1175,13 +1175,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>848.5</v>
+        <v>1176.9</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>357.3</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>316.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>175</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant BAES-RFP-106192: Task 1 Knowledge Management: 10 of 1642h = 164.2h; Grant MOSAICO: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1227,13 +1227,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1014.933333333333</v>
+        <v>1097.033333333333</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>407.5333333333333</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>268.2</v>
+        <v>350.3</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>339.2</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x assessor (8h each) = 104.0h; Grant CHEDDAR : Communications Hub for Empowering Distributed clouD computing Applications and Research - TMF uplift: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1435,13 +1435,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>844.5999999999999</v>
+        <v>1008.8</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>385.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>284.2</v>
+        <v>448.4</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>175</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 120.0h; Grant KTP with Advai: 5 of 1642h = 82.1h; Grant KTP with Advai (Industry): 0 of 1642h = 0.0h; Grant A STAR TO STEER BY: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1747,13 +1747,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>880.3400000000001</v>
+        <v>1126.64</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>50.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>540.2</v>
+        <v>786.5</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>289.94</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 376.0h; Grant BAES-RFP-106192: Task 1 Knowledge Management: 10 of 1642h = 164.2h; Grant MOSAICO: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1851,13 +1851,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>648.9666666666667</v>
+        <v>2143.186666666667</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>91.66666666666666</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>300.2</v>
+        <v>1794.42</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>257.1</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 136.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 11 of 1642h = 180.6h; Grant Centre of Excellence for Regulatory Science and Innovation in AI &amp; Digital Health Technologies (CERSI-AI): 80 of 1642h = 1313.6h</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1955,13 +1955,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1444</v>
+        <v>1608.2</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>99.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>348.2</v>
+        <v>512.4000000000001</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>996</v>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 184.0h; Grant BAES-RFP-106192: Task 3 SOA: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2007,13 +2007,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>603.2</v>
+        <v>1654.08</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>428.2</v>
+        <v>1479.08</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>175</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 264.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 264.0h; Grant Clinical Risk Management: Train the Trainer programme: 19 of 1642h = 312.0h; Grant AI and Digital Twins (with Alan Turing Institute) BRAID: 10 of 1642h = 164.2h; Grant Encoding Empathy: Solving the Healthcare Workforce Crisis Through the Safe Deployment of an AI-Driven Voice-Based Clinical Conversational Assistant for Long Term Monitoring: 10 of 1642h = 164.2h; Grant Addressing the healthcare workforce crisis with a multilingual, accessible phone-based conversational agent for cataract surgery follow up.: 10 of 1642h = 164.2h; Grant A STAR TO STEER BY: 5 of 1642h = 82.1h; Grant Qualifying Large Language Models for Oversight in Patient Safety Governance: 5 of 1642h = 82.1h; Grant Centre of Excellence for Regulatory Science and Innovation in AI &amp; Digital Health Technologies (CERSI-AI): 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2059,13 +2059,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>746.6333333333334</v>
+        <v>828.7333333333333</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>243.2333333333333</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>164.2</v>
+        <v>246.3</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>339.2</v>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>Grant EPSRC: Addressing environmental injustices through transdisciplinary science and technology: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2163,13 +2163,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>977.0666666666666</v>
+        <v>1469.666666666667</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>293.8666666666667</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>508.2</v>
+        <v>1000.8</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>175</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 5x assessor (8h each) = 344.0h; Grant ALL-VP: AI-Powered Lighting in Live Virtual Production: 20 of 1642h = 328.4h; Grant The DDS: The Data Donation Service for Games: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2371,13 +2371,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>565.3</v>
+        <v>1156.42</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>308.2</v>
+        <v>899.3199999999999</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>257.1</v>
@@ -2385,7 +2385,7 @@
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE = 144.0h; Grant Assessment of DSTA USVs and Continual Assurance of CI/CD for USVs: 5 of 1642h = 82.1h; Grant RAI UK: Safety &amp; Security Working Group (revised submission UKRI/CfAA): 20 of 1642h = 328.4h; Grant IMPA Tasking: Phase 1 Pilotage as a complex system: 11 of 1642h = 180.6h</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2523,13 +2523,13 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>826.3000000000001</v>
+        <v>990.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>349</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>220.2</v>
+        <v>384.4</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>257.1</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h</t>
+          <t>PhD supervision: 1x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 56.0h; Grant MOSAICO: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2627,16 +2627,16 @@
         <v>0.8</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>318.76</v>
+        <v>778.52</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>47.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>131.36</v>
+        <v>328.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>140</v>
+        <v>402.72</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
@@ -2645,12 +2645,12 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>No research activities recorded</t>
+          <t>Grant IMPA Tasking: Phase 1 Pilotage as a complex system: 7 of 1642h = 114.9h; Grant Qualifying Large Language Models for Oversight in Patient Safety Governance: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
+          <t>Ethics Committee Member: 20% of 1314h = 262.7h; Engagement (email/meetings): 80.0h; Personal development: 60.0h (FTE: 0.80)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>No administrative roles assigned</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 7x assessor (8h each) = 520.0h; Grant BiB Centre for Social Change: 0 of 1642h = 0.0h</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2939,13 +2939,13 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>967.9000000000001</v>
+        <v>1296.3</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>312.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>316.2</v>
+        <v>644.6</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>339.2</v>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h</t>
+          <t>PhD supervision: 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 152.0h; Grant Large Language Models for lattice-theoretic reasoning of reactive programs: 20 of 1642h = 328.4h</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2991,13 +2991,13 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1286.84</v>
+        <v>1763.02</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>312.3</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>356.2</v>
+        <v>832.3799999999999</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>618.34</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence: 9 of 1642h = 147.8h; Grant Establishing a Safe AI Research Hub: York–UTM–UTB Twin-Lab Initiative: 9 of 1642h = 147.8h; Grant PIE Programme for WiSE (Women in Sustainable and safE AI): 3 of 1642h = 49.3h; Grant Establishment of Korea–UK Collaboration Platform for Convergent Research in Quantum Photonics and Artificial Intelligence - Yr2: 5 of 1642h = 82.1h; Grant RAVEN-SCAR: Adaptive Robotics for XR Lighting Effects: 3 of 1642h = 49.3h</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -3095,13 +3095,13 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1386.333333333333</v>
+        <v>2207.333333333333</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>426.9333333333333</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>620.2</v>
+        <v>1441.2</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>339.2</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h</t>
+          <t>PhD supervision: 2x full-time PhD student × 80h/FTE; 6x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 456.0h; Grant CHEDDAR : Communications Hub for Empowering Distributed clouD computing Applications and Research - TMF uplift: 20 of 1642h = 328.4h; Grant CHEDDAR Extension 2025-26: 20 of 1642h = 328.4h; Grant CHEDDAR Funding Apr-Sep 26- PSU296: 5 of 1642h = 82.1h; Grant Orchestrated mobile Network for Blackpool intelligent transport: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -3199,13 +3199,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>847.0400000000001</v>
+        <v>2242.74</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>508.2</v>
+        <v>1903.9</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>207.84</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 5x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 344.0h; Grant CHEDDAR : Communications Hub for Empowering Distributed clouD computing Applications and Research - TMF uplift: 5 of 1642h = 82.1h; Grant DOMINOS: Disruption Mitigation for Responsible AI: 10 of 1642h = 164.2h; Grant Regulatory guidelines informing the societal and ethical factors shaping medical AI adoption: 0 of 1642h = 0.0h; Grant ULTIMATE: Universal Stochastic Modelling, Verification and Synthesis'?: 40 of 1642h = 656.8h; Grant Scaling the safe use of AI in automated driving systems: 10 of 1642h = 164.2h; Grant MammoBot: Robotic Posture Assistance for Universal Breast Screening Access: 10 of 1642h = 164.2h; Grant Boosting Ecosystem Resilience through Wood-Ant Colony Relocation: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -3251,13 +3251,13 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1051.9</v>
+        <v>1298.2</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>354.4</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>276.2</v>
+        <v>522.5</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>421.3</v>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 112.0h; Grant AID: Assuring the safe use of AI-enabled autonomy in nuclear Decommissioning: 10 of 1642h = 164.2h; Grant Rapid Insertion of Technology - Using AI to Streamline Safety Assurance (re-submission): 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -3407,13 +3407,13 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1104.363333333333</v>
+        <v>1186.463333333333</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>595.4833333333333</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>268.2</v>
+        <v>350.3</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>240.68</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant CHEDDAR : Communications Hub for Empowering Distributed clouD computing Applications and Research - TMF uplift: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3563,13 +3563,13 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1185.166666666667</v>
+        <v>1267.266666666667</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>367.6666666666666</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>396.2</v>
+        <v>478.3</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>421.3</v>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 232.0h; Grant Participatory Harm Auditing Workbenches &amp; Methodologies: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -3667,13 +3667,13 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>620.04</v>
+        <v>948.4400000000002</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>412.2</v>
+        <v>740.6000000000001</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>207.84</v>
@@ -3681,7 +3681,7 @@
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 3x assessor (8h each) = 248.0h; Grant GuardAI ( Enhancing Robustness and Security of Edge AI Systems for Safety-Critical Applications): 0 of 1642h = 0.0h; Grant ULTIMATE: Universal Stochastic Modelling, Verification and Synthesis'?: 20 of 1642h = 328.4h; Grant Cavecore: Doctoral Network on Continuous, Automated Validation, and Evaluation of Cognitive Robots in Open-Ended Environments: 0 of 1642h = 0.0h</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -3767,13 +3767,13 @@
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1118.15</v>
+        <v>1282.35</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>258.55</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>356.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>503.4</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE; 2x part-time PhD student × 48h/FTE; 2x assessor (8h each) = 192.0h; Grant Integrated Quantum Networks (IQN) Hub: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h</t>
+          <t>PhD supervision: 3x full-time PhD student × 80h/FTE; 1x part-time PhD student × 48h/FTE = 288.0h; Grant Northern Intensive Computing Environment: 0 of 1642h = 0.0h</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3871,13 +3871,13 @@
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1140.4</v>
+        <v>1271.76</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>368.8</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>268.2</v>
+        <v>399.56</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>503.4</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h</t>
+          <t>PhD supervision: 2x part-time PhD student × 48h/FTE; 1x assessor (8h each) = 104.0h; Grant RAVEN-SCAR: Adaptive Robotics for XR Lighting Effects: 8 of 1642h = 131.4h</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -4027,13 +4027,13 @@
         <v>1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1424.216666666667</v>
+        <v>1834.716666666667</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>367.7666666666667</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>676.2</v>
+        <v>1086.7</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>380.25</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h</t>
+          <t>PhD supervision: 4x full-time PhD student × 80h/FTE; 3x part-time PhD student × 48h/FTE; 6x assessor (8h each) = 512.0h; Grant ALL-VP: AI-Powered Lighting in Live Virtual Production: 20 of 1642h = 328.4h; Grant Proglacial lakes as drivers of glacier retreat and hydrological (in)stability: 5 of 1642h = 82.1h</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -4079,13 +4079,13 @@
         <v>1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>893.1</v>
+        <v>1057.3</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>391.8</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>244.2</v>
+        <v>408.4</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>257.1</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h</t>
+          <t>PhD supervision: 1x full-time PhD student × 80h/FTE = 80.0h; Grant WATERS: Worldwide AquaTic chemical Exposure and Risk System: 10 of 1642h = 164.2h</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>548.2</v>
+        <v>712.4000000000001</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>257.1</v>
@@ -4345,7 +4345,7 @@
         <v>357.3</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>316.2</v>
+        <v>644.6000000000001</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>175</v>
@@ -4365,7 +4365,7 @@
         <v>407.5333333333333</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>268.2</v>
+        <v>350.3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>339.2</v>
@@ -4445,7 +4445,7 @@
         <v>385.4</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>284.2</v>
+        <v>448.4</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>175</v>
@@ -4565,7 +4565,7 @@
         <v>50.2</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>540.2</v>
+        <v>786.5</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>289.94</v>
@@ -4605,7 +4605,7 @@
         <v>91.66666666666666</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>300.2</v>
+        <v>1794.42</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>257.1</v>
@@ -4645,7 +4645,7 @@
         <v>99.8</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>348.2</v>
+        <v>512.4000000000001</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>996</v>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>428.2</v>
+        <v>1479.08</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>175</v>
@@ -4685,7 +4685,7 @@
         <v>243.2333333333333</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>164.2</v>
+        <v>246.3</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>339.2</v>
@@ -4725,7 +4725,7 @@
         <v>293.8666666666667</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>508.2</v>
+        <v>1000.8</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>175</v>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>308.2</v>
+        <v>899.3199999999999</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>257.1</v>
@@ -4865,7 +4865,7 @@
         <v>349</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>220.2</v>
+        <v>384.4</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>257.1</v>
@@ -4905,10 +4905,10 @@
         <v>47.4</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>131.36</v>
+        <v>328.4</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>140</v>
+        <v>402.72</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(B35:D35)</f>
@@ -5025,7 +5025,7 @@
         <v>312.5</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>316.2</v>
+        <v>644.6</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>339.2</v>
@@ -5045,7 +5045,7 @@
         <v>312.3</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>356.2</v>
+        <v>832.3799999999999</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>618.34</v>
@@ -5085,7 +5085,7 @@
         <v>426.9333333333333</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>620.2</v>
+        <v>1441.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>339.2</v>
@@ -5125,7 +5125,7 @@
         <v>131</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>508.2</v>
+        <v>1903.9</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>207.84</v>
@@ -5145,7 +5145,7 @@
         <v>354.4</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>276.2</v>
+        <v>522.5</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>421.3</v>
@@ -5205,7 +5205,7 @@
         <v>595.4833333333333</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>268.2</v>
+        <v>350.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>240.68</v>
@@ -5265,7 +5265,7 @@
         <v>367.6666666666666</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>396.2</v>
+        <v>478.3</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>421.3</v>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>412.2</v>
+        <v>740.6000000000001</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>207.84</v>
@@ -5345,7 +5345,7 @@
         <v>258.55</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>356.2</v>
+        <v>520.4000000000001</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>503.4</v>
@@ -5385,7 +5385,7 @@
         <v>368.8</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>268.2</v>
+        <v>399.56</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>503.4</v>
@@ -5445,7 +5445,7 @@
         <v>367.7666666666667</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>676.2</v>
+        <v>1086.7</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>380.25</v>
@@ -5465,7 +5465,7 @@
         <v>391.8</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>244.2</v>
+        <v>408.4</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>257.1</v>

--- a/baseline/Staff workload model.xlsx
+++ b/baseline/Staff workload model.xlsx
@@ -919,10 +919,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1112.8</v>
+        <v>1142.8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>443.5</v>
+        <v>473.5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>412.2</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Adrian Bors: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 11 projects x UG (16h) = 176.0h</t>
+          <t>NLPG (20cr): Adrian Bors: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 8 UG x 16h = 128.0h; 3 PGT x 24h = 72.0h; setting 6.0h = 206.0h</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1266.6</v>
+        <v>1312.6</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>319</v>
+        <v>365</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>444.2</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PLEI (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>IDEV (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PLEI (20cr): Alena Denisova: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 27 students x 3h = 81.0h; Projects: 5 PGT x 24h = 120.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -1023,10 +1023,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>927.2333333333333</v>
+        <v>941.2333333333333</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>319.8333333333333</v>
+        <v>333.8333333333333</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>268.2</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Alvaro Miyazawa: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ARIA (20cr): Alvaro Miyazawa: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; AURO (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; THE2 (20cr): Alvaro Miyazawa: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 3 UG x 16h = 48.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 78.0h</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1123,10 +1123,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>816.9333333333333</v>
+        <v>838.9333333333333</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>395.6333333333333</v>
+        <v>417.6333333333333</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>164.2</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 11 students x 3h = 33.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>SYS1 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SYS2 (20cr): Andrew Pomfret: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Pastoral: 11 students x 3h = 33.0h; Projects: 3 UG x 16h = 48.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 102.0h</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1176.9</v>
+        <v>1190.9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>357.3</v>
+        <v>371.3</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>644.6000000000001</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>ELLA (20cr): Antonio Garcia-Dominguez: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Antonio Garcia-Dominguez: 5x, &lt;new hire&gt;: 7.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ELLA (20cr): Antonio Garcia-Dominguez: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Antonio Garcia-Dominguez: 5x, &lt;new hire&gt;: 7.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ENG2 (20cr): Antonio Garcia-Dominguez: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 12 students x 3h = 36.0h; Projects: 3 UG x 16h = 48.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 78.0h</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1227,10 +1227,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1097.033333333333</v>
+        <v>1135.033333333333</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>407.5333333333333</v>
+        <v>445.5333333333333</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>350.3</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>CTAP (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; PRAD (20cr): Carlo Ottaviani: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 2 UG x 16h = 32.0h; 4 PGT x 24h = 96.0h; setting 6.0h = 134.0h</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1279,10 +1279,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1219.65</v>
+        <v>1241.65</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>593.1</v>
+        <v>615.1</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>164.2</v>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>SYS2 (20cr): Christopher Crispin-Bailey: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS3 (20cr): Christopher Crispin-Bailey: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 19 students x 3h = 57.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SYS2 (20cr): Christopher Crispin-Bailey: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Andrew Pomfret: 2.5x, Mike Freeman: 2.5x, Christopher Crispin-Bailey: 5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS3 (20cr): Christopher Crispin-Bailey: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 19 students x 3h = 57.0h; Projects: 5 UG x 16h = 80.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 134.0h</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1331,10 +1331,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>820.9</v>
+        <v>778.9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>399.6</v>
+        <v>357.6</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>164.2</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 10 projects x MSc (24h) = 240.0h</t>
+          <t>HINT (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Claire Ingram: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 1 students x 3h = 3.0h; Projects: 6 UG x 16h = 96.0h; 4 PGT x 24h = 96.0h; setting 6.0h = 198.0h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1383,10 +1383,10 @@
         <v>0.4</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>444.5466666666667</v>
+        <v>450.5466666666667</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>196.8666666666667</v>
+        <v>202.8666666666667</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>177.68</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>IMLO (20cr): Claudio Guarnera: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 10 students x 3h = 30.0h; Projects: 2 UG x 16h = 32.0h; setting 6.0h = 38.0h</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1435,10 +1435,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1008.8</v>
+        <v>1030.8</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>385.4</v>
+        <v>407.4</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>448.4</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Colin Paterson: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 6 projects x UG (16h) = 96.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
+          <t>LPTC (20cr): Colin Paterson: Standard (2.5x): 0.0h/teacher @ 2.5x; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Colin Paterson: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 19 students x 3h = 57.0h; Projects: 4 UG x 16h = 64.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 118.0h; Also teaches: Designing Safe AI (Safe AI 2) (SAINTS - not included in workload)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1591,10 +1591,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>816</v>
+        <v>846</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>476.8</v>
+        <v>506.8</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>164.2</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 11 projects x UG (16h) = 176.0h</t>
+          <t>SOF1 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Dawn H Wood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 8 UG x 16h = 128.0h; 3 PGT x 24h = 72.0h; setting 6.0h = 206.0h</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1643,10 +1643,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1152.983333333333</v>
+        <v>1174.983333333333</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>389.3833333333333</v>
+        <v>411.3833333333333</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>260.2</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>THE2 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Detlef Plump: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 4 UG x 16h = 64.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 118.0h</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1695,10 +1695,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1510.4</v>
+        <v>1532.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>386.8</v>
+        <v>408.8</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>620.2</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>NLPG (20cr): Dimitar Kazakov: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>NLPG (20cr): Dimitar Kazakov: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - 5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 5 UG x 16h = 80.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 134.0h</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -2059,10 +2059,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>828.7333333333333</v>
+        <v>842.7333333333333</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>243.2333333333333</v>
+        <v>257.2333333333333</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>246.3</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>HCIN (20cr): Jacob Rigby: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 8 students x 3h = 24.0h; Projects: 4 UG x 16h = 64.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 94.0h</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2163,10 +2163,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1469.666666666667</v>
+        <v>1475.666666666667</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>293.8666666666667</v>
+        <v>299.8666666666667</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1000.8</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>IMLO (20cr): James Walker: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: James Stovold: 5x, Claudio Guarnera: 2.5x, James Walker: 2.5x; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 21 students x 3h = 63.0h; Projects: 6 UG x 16h = 96.0h; setting 6.0h = 102.0h</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2215,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1275.5</v>
+        <v>1289.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>275.7</v>
+        <v>289.7</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>332.2</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>QUAL (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; TECC (20cr): Jen Beeston: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 3 UG x 16h = 48.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 78.0h</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2267,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>969.1</v>
+        <v>1007.1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>281.7</v>
+        <v>319.7</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>348.2</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>PLEI (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; QUAL (20cr): Jo Iacovides: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 12 students x 3h = 36.0h; Projects: 2 UG x 16h = 32.0h; 4 PGT x 24h = 96.0h; setting 6.0h = 134.0h</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2319,10 +2319,10 @@
         <v>1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>750.3</v>
+        <v>772.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>347.1</v>
+        <v>369.1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>228.2</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>IDEV (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; PRAD (20cr): Joe Cutting: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 16 students x 3h = 48.0h; Projects: 5 UG x 16h = 80.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 134.0h</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2419,10 +2419,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1122.233333333333</v>
+        <v>1136.233333333333</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>406.6333333333333</v>
+        <v>420.6333333333333</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>212.2</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>HCIN (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; TECC (20cr): Katrina Attwood: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 22 students x 3h = 66.0h; Projects: 5 UG x 16h = 80.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 110.0h</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2471,10 +2471,10 @@
         <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1205.3</v>
+        <v>1219.3</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>427.8</v>
+        <v>441.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>356.2</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>SOF1 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; SOF2 (20cr): Kofi Appiah: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Kofi Appiah: 2.5x, Dawn H Wood: 2.5x, Fang Yan: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 18 students x 3h = 54.0h; Projects: 6 UG x 16h = 96.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2523,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>990.5</v>
+        <v>996.5</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>384.4</v>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>ENG1 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; ENG2 (20cr): Kostas Barmpis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 22 students x 3h = 66.0h; Projects: 2 UG x 16h = 32.0h; setting 6.0h = 38.0h</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2575,10 +2575,10 @@
         <v>0.8</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>662.6039999999999</v>
+        <v>668.6039999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>242.7</v>
+        <v>248.7</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>227.36</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
+          <t>RASS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SSAS (10cr): Mark Nicholson: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 5 PGT x 24h = 120.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2731,10 +2731,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>928.6</v>
+        <v>950.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>507.3</v>
+        <v>529.3</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>164.2</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>CBDA (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; GODS (20cr): Mike O'Dea: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; ROCS (20cr): Mike O'Dea: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Projects: 5 UG x 16h = 80.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 134.0h</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2783,10 +2783,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1468.933333333333</v>
+        <v>1482.933333333333</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>208.9333333333333</v>
+        <v>222.9333333333333</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>428.2</v>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>THE1 (20cr): Nick Pears: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 3 UG x 16h = 48.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 78.0h</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2835,10 +2835,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>725.3</v>
+        <v>731.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>164.2</v>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 5 projects x MSc (24h) = 120.0h</t>
+          <t>FSSE (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; HRAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SSAS (10cr): Oleg Lisagor: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 5 PGT x 24h = 120.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2887,10 +2887,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1451.133333333333</v>
+        <v>1473.133333333333</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>345.6333333333333</v>
+        <v>367.6333333333333</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>684.2</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>GODS (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HCIN (20cr): Paul Cairns: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; Pastoral: 5 students x 3h = 15.0h; Projects: 4 UG x 16h = 64.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 118.0h</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2939,10 +2939,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1296.3</v>
+        <v>1318.3</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>312.5</v>
+        <v>334.5</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>644.6</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>AURO (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; SYS1 (20cr): Pedro Ribeiro: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 2 UG x 16h = 32.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 86.0h</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2991,10 +2991,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1763.02</v>
+        <v>1777.02</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>312.3</v>
+        <v>326.3</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>832.3799999999999</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>SYS3 (20cr): Pengcheng Liu: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 10 students x 3h = 30.0h; Projects: 3 UG x 16h = 48.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 78.0h</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3043,10 +3043,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1069.866666666667</v>
+        <v>1083.866666666667</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>430.4666666666666</v>
+        <v>444.4666666666666</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>300.2</v>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>ARIA (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; FOAM (20cr): Peter Nightingale: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SAIL (20cr): Peter Nightingale: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 4 UG x 16h = 64.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 94.0h</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3095,10 +3095,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2207.333333333333</v>
+        <v>2221.333333333333</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>426.9333333333333</v>
+        <v>440.9333333333333</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1441.2</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 13 projects x UG (16h) = 208.0h</t>
+          <t>SOF1 (20cr): Poonam Yadav: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 25 students x 3h = 75.0h; Projects: 12 UG x 16h = 192.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 222.0h</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3147,10 +3147,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>978.9</v>
+        <v>984.9</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>452.55</v>
+        <v>458.55</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>228.2</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>DATA (20cr): Pourya Shamsolmoali: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; DEEP (20cr): Pourya Shamsolmoali: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; Pastoral: 5 students x 3h = 15.0h; Projects: 2 UG x 16h = 32.0h; setting 6.0h = 38.0h</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3199,10 +3199,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2242.74</v>
+        <v>2256.740000000001</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>1903.9</v>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 projects x UG (16h) = 16.0h</t>
+          <t>GPIG (40cr): Radu Calinescu: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 1 PGT x 24h = 24.0h; setting 6.0h = 30.0h</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3251,10 +3251,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1298.2</v>
+        <v>1272.2</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>354.4</v>
+        <v>328.4</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>522.5</v>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
+          <t>CASA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SCDR (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Richard Hawkins: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 23 students x 3h = 69.0h; Projects: 4 UG x 16h = 64.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 118.0h</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3355,10 +3355,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>937.78</v>
+        <v>911.78</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>380.9</v>
+        <v>354.9</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>316.2</v>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
+          <t>HINT (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; RASS (10cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; REMS (20cr): Rob Alexander: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 13 students x 3h = 39.0h; Projects: 4 UG x 16h = 64.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 118.0h</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3407,10 +3407,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1186.463333333333</v>
+        <v>1216.463333333333</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>595.4833333333333</v>
+        <v>625.4833333333333</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>350.3</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>CBDA (20cr): Roberto Metere: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: Mike O'Dea: 2.5x, Roberto Metere: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; CTAP (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; EHAC (20cr): Roberto Metere: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 20 students x 3h = 60.0h; Projects: 3 UG x 16h = 48.0h; 3 PGT x 24h = 72.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3459,10 +3459,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>623.7833333333333</v>
+        <v>637.7833333333333</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>284.5833333333333</v>
+        <v>298.5833333333333</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>164.2</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 7 projects x UG (16h) = 112.0h</t>
+          <t>QUCO (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; THE2 (20cr): Sam Braunstein: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 4 students x 3h = 12.0h; Projects: 6 UG x 16h = 96.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -3511,10 +3511,10 @@
         <v>0.8</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>600.66</v>
+        <v>606.66</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>329.3</v>
+        <v>335.3</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>131.36</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 8 projects x MSc (24h) = 192.0h</t>
+          <t>FSSE (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; SCDR (10cr): Sarah Carrington: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 8 PGT x 24h = 192.0h; setting 6.0h = 198.0h</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -3563,10 +3563,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1267.266666666667</v>
+        <v>1297.266666666667</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>367.6666666666666</v>
+        <v>397.6666666666666</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>478.3</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>CTAP (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 3.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE1 (20cr): Siamak Shahandashti: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Pastoral: 17 students x 3h = 51.0h; Projects: 3 UG x 16h = 48.0h; 3 PGT x 24h = 72.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3615,10 +3615,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>823.1166666666666</v>
+        <v>829.1166666666666</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>371.9166666666666</v>
+        <v>377.9166666666666</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>276.2</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 2 projects x UG (16h) = 32.0h</t>
+          <t>THE1 (20cr): Simon Foster: New lecturer (5x): 0.0h base @ 2.5x + 0.0h content dev; First time delivery: 1 sessions/week @ 1.0h each; - Per-teacher rates applied: Simon Foster: 5x, Nick Pears: 2.5x, Siamak Shahandashti: 2.5x; New setter (15h/assess, manual): 2.5h main + 2.5h resit = 7.5h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; THE3 (20cr): Simon Foster: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 1.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Pastoral: 11 students x 3h = 33.0h; Projects: 2 UG x 16h = 32.0h; setting 6.0h = 38.0h</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -3767,10 +3767,10 @@
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1282.35</v>
+        <v>1312.35</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>258.55</v>
+        <v>288.55</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>520.4000000000001</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>QUCO (20cr): Stefano Pirandola: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 3 UG x 16h = 48.0h; 3 PGT x 24h = 72.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3819,10 +3819,10 @@
         <v>1</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1353.8</v>
+        <v>1367.8</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>452.2</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>HIPC (20cr): Steven Wright: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 14 students x 3h = 42.0h; Projects: 3 UG x 16h = 48.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 78.0h</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3871,10 +3871,10 @@
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1271.76</v>
+        <v>1285.76</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>368.8</v>
+        <v>382.8</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>399.56</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>EMBS (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; HIPC (20cr): Steven Xiaotian Dai: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 15 students x 3h = 45.0h; Projects: 5 UG x 16h = 80.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 110.0h</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3923,10 +3923,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1477.546666666667</v>
+        <v>1515.546666666667</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>544.2666666666667</v>
+        <v>582.2666666666667</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>364.2</v>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 4 projects x UG (16h) = 64.0h</t>
+          <t>ARIA (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; Standard (15h/assess, manual): 2.5h main + 2.5h resit = 5.0h; ENG1 (20cr): Tommy Yuan: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; FOAM (20cr): Tommy Yuan: Existing lecturer + new content (5x): 0.0h base @ 2.5x + 0.0h content dev; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 18 students x 3h = 54.0h; Projects: 4 PGT x 24h = 96.0h; setting 6.0h = 102.0h</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3975,10 +3975,10 @@
         <v>1</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1079.9</v>
+        <v>1061.9</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>384.5</v>
+        <v>366.5</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>356.2</v>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 6 projects x MSc (24h) = 144.0h</t>
+          <t>NETS (20cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; SESA (10cr): Vasileios Vasilakis: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 26 students x 3h = 78.0h; Projects: 3 UG x 16h = 48.0h; 3 PGT x 24h = 72.0h; setting 6.0h = 126.0h</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4027,10 +4027,10 @@
         <v>1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1834.716666666667</v>
+        <v>1848.716666666667</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>367.7666666666667</v>
+        <v>381.7666666666667</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>1086.7</v>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>DEEP (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Pourya Shamsolmoali: 5x; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; New setter (15h/assess, manual): 3.8h main + 3.8h resit = 11.2h; ROCS (20cr): William Smith: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - Per-teacher rates applied: William Smith: 2.5x, Mike O'Dea: 5x, Colin Paterson: 5x; Standard (15h/assess, manual): 5.0h main + 5.0h resit = 10.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; New setter (15h/assess, manual): 5.0h main + 5.0h resit = 15.0h; Pastoral: 7 students x 3h = 21.0h; Projects: 5 UG x 16h = 80.0h; 1 PGT x 24h = 24.0h; setting 6.0h = 110.0h</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4079,10 +4079,10 @@
         <v>1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1057.3</v>
+        <v>1087.3</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>391.8</v>
+        <v>421.8</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>408.4</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 5 projects x UG (16h) = 80.0h</t>
+          <t>DATA (20cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; GPIG (40cr): Xinwei Fang: Standard (2.5x): 0.0h/teacher @ 2.5x; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Standard (15h/assess, manual): 11.2h main + 11.2h resit = 22.5h; Pastoral: 9 students x 3h = 27.0h; Projects: 2 UG x 16h = 32.0h; 3 PGT x 24h = 72.0h; setting 6.0h = 110.0h</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -4131,10 +4131,10 @@
         <v>1</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>840.5</v>
+        <v>862.5</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>403.2</v>
+        <v>425.2</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>180.2</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 6 projects x UG (16h) = 96.0h</t>
+          <t>EHAC (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; Standard (15h/assess, manual): 7.5h main + 7.5h resit = 15.0h; NETS (20cr): Yuchen Zhao: Standard (2.5x): 0.0h/teacher @ 2.5x; First time delivery: 1 sessions/week @ 2.0h each; - 2.5x lecturer rate applied (first session: 2.5x, repeats: 1.5x); Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Standard (15h/assess, manual): 3.8h main + 3.8h resit = 7.5h; Pastoral: 25 students x 3h = 75.0h; Projects: 4 UG x 16h = 64.0h; 2 PGT x 24h = 48.0h; setting 6.0h = 118.0h</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>443.5</v>
+        <v>473.5</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>412.2</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>319</v>
+        <v>365</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>444.2</v>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>319.8333333333333</v>
+        <v>333.8333333333333</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>268.2</v>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>395.6333333333333</v>
+        <v>417.6333333333333</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>164.2</v>
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>357.3</v>
+        <v>371.3</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>644.6000000000001</v>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>407.5333333333333</v>
+        <v>445.5333333333333</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>350.3</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>593.1</v>
+        <v>615.1</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>164.2</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>399.6</v>
+        <v>357.6</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>164.2</v>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>196.8666666666667</v>
+        <v>202.8666666666667</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>177.68</v>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>385.4</v>
+        <v>407.4</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>448.4</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>476.8</v>
+        <v>506.8</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>164.2</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>389.3833333333333</v>
+        <v>411.3833333333333</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>260.2</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>386.8</v>
+        <v>408.8</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>620.2</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>243.2333333333333</v>
+        <v>257.2333333333333</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>246.3</v>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>293.8666666666667</v>
+        <v>299.8666666666667</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>1000.8</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>275.7</v>
+        <v>289.7</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>332.2</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>281.7</v>
+        <v>319.7</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>348.2</v>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>347.1</v>
+        <v>369.1</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>228.2</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>406.6333333333333</v>
+        <v>420.6333333333333</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>212.2</v>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>427.8</v>
+        <v>441.8</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>356.2</v>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>384.4</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>242.7</v>
+        <v>248.7</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>227.36</v>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>507.3</v>
+        <v>529.3</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>164.2</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>208.9333333333333</v>
+        <v>222.9333333333333</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>428.2</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>164.2</v>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>345.6333333333333</v>
+        <v>367.6333333333333</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>684.2</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>312.5</v>
+        <v>334.5</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>644.6</v>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>312.3</v>
+        <v>326.3</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>832.3799999999999</v>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>430.4666666666666</v>
+        <v>444.4666666666666</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>300.2</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>426.9333333333333</v>
+        <v>440.9333333333333</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>1441.2</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>452.55</v>
+        <v>458.55</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>228.2</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>1903.9</v>
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>354.4</v>
+        <v>328.4</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>522.5</v>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>380.9</v>
+        <v>354.9</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>316.2</v>
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>595.4833333333333</v>
+        <v>625.4833333333333</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>350.3</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>284.5833333333333</v>
+        <v>298.5833333333333</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>164.2</v>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>329.3</v>
+        <v>335.3</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>131.36</v>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>367.6666666666666</v>
+        <v>397.6666666666666</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>478.3</v>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>371.9166666666666</v>
+        <v>377.9166666666666</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>276.2</v>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>258.55</v>
+        <v>288.55</v>
       </c>
       <c r="C57" s="7" t="n">
         <v>520.4000000000001</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="B58" s="7" t="n">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C58" s="7" t="n">
         <v>452.2</v>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>368.8</v>
+        <v>382.8</v>
       </c>
       <c r="C59" s="7" t="n">
         <v>399.56</v>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>544.2666666666667</v>
+        <v>582.2666666666667</v>
       </c>
       <c r="C60" s="7" t="n">
         <v>364.2</v>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>384.5</v>
+        <v>366.5</v>
       </c>
       <c r="C61" s="7" t="n">
         <v>356.2</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>367.7666666666667</v>
+        <v>381.7666666666667</v>
       </c>
       <c r="C62" s="7" t="n">
         <v>1086.7</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>391.8</v>
+        <v>421.8</v>
       </c>
       <c r="C63" s="7" t="n">
         <v>408.4</v>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>403.2</v>
+        <v>425.2</v>
       </c>
       <c r="C64" s="7" t="n">
         <v>180.2</v>
